--- a/ABA_mining/outputs/eval/task3/check-out/llama3.2/contrary_v6/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/check-out/llama3.2/contrary_v6/EVAL_SUMMARY.xlsx
@@ -547,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O2" t="n">
         <v>0.625</v>
@@ -606,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O3" t="n">
         <v>0.625</v>
@@ -665,7 +665,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O4" t="n">
         <v>0.625</v>
@@ -790,7 +790,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="I2" t="n">
         <v>0.625</v>
